--- a/tools/importer/reports/import-home.report.xlsx
+++ b/tools/importer/reports/import-home.report.xlsx
@@ -52,7 +52,7 @@
     <t>home</t>
   </si>
   <si>
-    <t>2026-10-21T12:05:46.209Z</t>
+    <t>2026-10-21T19:54:05.566Z</t>
   </si>
   <si>
     <t>Exceptional Care Any Time, Any Where | Advocate Health Care:</t>
